--- a/artfynd/A 25524-2024 artfynd.xlsx
+++ b/artfynd/A 25524-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>117978665</v>
       </c>
       <c r="B4" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25524-2024 artfynd.xlsx
+++ b/artfynd/A 25524-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117239173</v>
+        <v>117239174</v>
       </c>
       <c r="B2" t="n">
-        <v>90464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>819006</v>
+        <v>818967</v>
       </c>
       <c r="R2" t="n">
-        <v>7286130</v>
+        <v>7286147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117239174</v>
+        <v>117239173</v>
       </c>
       <c r="B3" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>818967</v>
+        <v>819006</v>
       </c>
       <c r="R3" t="n">
-        <v>7286147</v>
+        <v>7286130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117978665</v>
+        <v>117178385</v>
       </c>
       <c r="B4" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Måttsund 37:1, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>818931</v>
+        <v>818957</v>
       </c>
       <c r="R4" t="n">
-        <v>7286099</v>
+        <v>7286186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,6 +963,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117978665</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Måttsund 37:1, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>818931</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7286099</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25524-2024 artfynd.xlsx
+++ b/artfynd/A 25524-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117239174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117239173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117178385</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117978665</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>